--- a/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0002T0006Z000C1N47_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0002T0006Z000C1N47_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>40.14538057781545</v>
+        <v>6.523624343895011</v>
       </c>
       <c r="D2" t="n">
-        <v>25.49664563426222</v>
+        <v>4.143204915567611</v>
       </c>
       <c r="E2" t="n">
-        <v>5.351756772543116</v>
+        <v>0.869660475538256</v>
       </c>
       <c r="F2" t="n">
-        <v>11.09791894841324</v>
+        <v>1.803411829117151</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>47.49588960204836</v>
+        <v>7.718082060332859</v>
       </c>
       <c r="D3" t="n">
-        <v>46.0553644002296</v>
+        <v>7.483996715037311</v>
       </c>
       <c r="E3" t="n">
-        <v>5.351756772543116</v>
+        <v>0.869660475538256</v>
       </c>
       <c r="F3" t="n">
-        <v>11.09791894841324</v>
+        <v>1.803411829117151</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>53.22081409352423</v>
+        <v>8.648382290197686</v>
       </c>
       <c r="D4" t="n">
-        <v>51.1786487663355</v>
+        <v>8.316530424529519</v>
       </c>
       <c r="E4" t="n">
-        <v>5.351756772543116</v>
+        <v>0.869660475538256</v>
       </c>
       <c r="F4" t="n">
-        <v>11.09791894841324</v>
+        <v>1.803411829117151</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
